--- a/Data/IceStation1a/10jul2025coring/20250710-PS149_13-1-SI_corer_9cm-018-FYI-SALO18.xlsx
+++ b/Data/IceStation1a/10jul2025coring/20250710-PS149_13-1-SI_corer_9cm-018-FYI-SALO18.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dima\Documents\proposals\Contrasts_JulAug2025\IceStation1\10jul2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dima\Documents\proposals\Contrasts_JulAug2025\IceStation1a\10jul2025coring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CFB7CD-D661-41F8-821C-DFC98B34035D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444A7644-6D7B-4193-8756-5779A2CE0B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="726" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="726" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="342">
   <si>
     <t>Core</t>
   </si>
@@ -938,9 +938,6 @@
     <t>UTC+12</t>
   </si>
   <si>
-    <t>20250710-PS_149-FYI</t>
-  </si>
-  <si>
     <t>large crystals, granular ice/scatter layer</t>
   </si>
   <si>
@@ -1008,6 +1005,75 @@
   </si>
   <si>
     <t>CONTRATS-PS_149</t>
+  </si>
+  <si>
+    <t>20250710-PS149_13-1-SI_corer_9cm-019-FYI-T</t>
+  </si>
+  <si>
+    <t>20250710-PS149_13-1-SI_corer_9cm-017-FYI-RHO</t>
+  </si>
+  <si>
+    <t>Dmitry Divine</t>
+  </si>
+  <si>
+    <t>Emiliano Cimoli</t>
+  </si>
+  <si>
+    <t>20250710-PS149_13-1-SI_corer_9cm-018-FYI-SALO18</t>
+  </si>
+  <si>
+    <t>20250710-PS149_13-1-SI_corer_9cm-016-FYI-REP</t>
+  </si>
+  <si>
+    <t>20250710-PS149_13-1-SI_corer_9cm-020-FYI-TEX</t>
+  </si>
+  <si>
+    <t>PS149-DO18-001</t>
+  </si>
+  <si>
+    <t>PS149-DO18-002</t>
+  </si>
+  <si>
+    <t>PS149-DO18-003</t>
+  </si>
+  <si>
+    <t>PS149-DO18-004</t>
+  </si>
+  <si>
+    <t>PS149-DO18-005</t>
+  </si>
+  <si>
+    <t>PS149-DO18-006</t>
+  </si>
+  <si>
+    <t>PS149-DO18-007</t>
+  </si>
+  <si>
+    <t>PS149-DO18-008</t>
+  </si>
+  <si>
+    <t>PS149-DO18-009</t>
+  </si>
+  <si>
+    <t>PS149-DO18-010</t>
+  </si>
+  <si>
+    <t>PS149-DO18-011</t>
+  </si>
+  <si>
+    <t>PS149-DO18-012</t>
+  </si>
+  <si>
+    <t>PS149-DO18-013</t>
+  </si>
+  <si>
+    <t>PS149-DO18-014</t>
+  </si>
+  <si>
+    <t>PS149-DO18-015</t>
+  </si>
+  <si>
+    <t>conductivity probe 67953, S/N 11440477</t>
   </si>
 </sst>
 </file>
@@ -1596,11 +1662,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1611,22 +1690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1635,7 +1699,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1644,17 +1708,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1665,7 +1732,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="4" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Excel Built-in Calculation" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -21479,11 +21545,11 @@
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="143" t="s">
-        <v>296</v>
-      </c>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
+      <c r="C1" s="144" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
       <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:7" ht="14.4">
@@ -21519,9 +21585,9 @@
       <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:7">
@@ -21602,7 +21668,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -21628,12 +21694,15 @@
         <v>15</v>
       </c>
       <c r="B13" s="19"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
     </row>
     <row r="14" spans="1:7">
+      <c r="A14" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -21736,10 +21805,10 @@
       </c>
       <c r="P1" s="19"/>
       <c r="Q1" s="9"/>
-      <c r="R1" s="161" t="s">
+      <c r="R1" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="S1" s="161"/>
+      <c r="S1" s="160"/>
       <c r="T1" s="9"/>
       <c r="U1" s="58" t="s">
         <v>85</v>
@@ -21749,16 +21818,16 @@
       </c>
       <c r="W1" s="19"/>
       <c r="X1" s="9"/>
-      <c r="Y1" s="163" t="s">
+      <c r="Y1" s="164" t="s">
         <v>142</v>
       </c>
-      <c r="Z1" s="163"/>
-      <c r="AA1" s="163"/>
+      <c r="Z1" s="164"/>
+      <c r="AA1" s="164"/>
       <c r="AB1" s="9"/>
-      <c r="AC1" s="164" t="s">
+      <c r="AC1" s="165" t="s">
         <v>143</v>
       </c>
-      <c r="AD1" s="164"/>
+      <c r="AD1" s="165"/>
       <c r="AE1" s="9"/>
     </row>
     <row r="2" spans="1:31" ht="41.4">
@@ -25562,12 +25631,12 @@
       <c r="H1" s="137" t="s">
         <v>175</v>
       </c>
-      <c r="I1" s="165" t="s">
+      <c r="I1" s="166" t="s">
         <v>176</v>
       </c>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="165"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="137" t="s">
         <v>177</v>
       </c>
@@ -26061,13 +26130,13 @@
       <c r="Y1" s="22"/>
     </row>
     <row r="2" spans="1:25" ht="12.75" customHeight="1">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -26094,11 +26163,11 @@
         <v>20</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="149" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
+      <c r="C3" s="146" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -26125,11 +26194,11 @@
         <v>21</v>
       </c>
       <c r="B4" s="26"/>
-      <c r="C4" s="150" t="s">
-        <v>299</v>
-      </c>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
+      <c r="C4" s="147" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -26152,13 +26221,13 @@
       <c r="Y4" s="22"/>
     </row>
     <row r="5" spans="1:25" ht="25.95" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="22"/>
@@ -26183,16 +26252,16 @@
     <row r="6" spans="1:25" ht="13.5" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="151" t="s">
+      <c r="C6" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="144" t="s">
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="144"/>
-      <c r="H6" s="144"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
       <c r="I6" s="4"/>
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
@@ -26318,17 +26387,17 @@
       <c r="Y9" s="22"/>
     </row>
     <row r="10" spans="1:25" ht="23.4" customHeight="1">
-      <c r="A10" s="148" t="s">
+      <c r="A10" s="149" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="148"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="148"/>
-      <c r="E10" s="148"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
       <c r="L10" s="22"/>
@@ -26483,13 +26552,13 @@
       <c r="Y14" s="22"/>
     </row>
     <row r="15" spans="1:25" ht="24.15" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
-      <c r="E15" s="148"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -26766,13 +26835,13 @@
       <c r="Y23" s="22"/>
     </row>
     <row r="24" spans="1:25" ht="26.4" customHeight="1">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -26935,13 +27004,13 @@
       <c r="Y28" s="22"/>
     </row>
     <row r="29" spans="1:25" ht="24.15" customHeight="1">
-      <c r="A29" s="144" t="s">
+      <c r="A29" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="144"/>
-      <c r="C29" s="144"/>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
+      <c r="B29" s="145"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
@@ -26969,7 +27038,7 @@
       </c>
       <c r="B30" s="51"/>
       <c r="C30" s="48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -26999,11 +27068,21 @@
         <v>65</v>
       </c>
       <c r="B31" s="51"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
+      <c r="C31" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>323</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>325</v>
+      </c>
       <c r="H31" s="52"/>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -27028,7 +27107,12 @@
         <v>66</v>
       </c>
       <c r="B32" s="51"/>
-      <c r="C32" s="48"/>
+      <c r="C32" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="D32" t="s">
+        <v>322</v>
+      </c>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
       <c r="J32" s="22"/>
@@ -27053,11 +27137,11 @@
         <v>67</v>
       </c>
       <c r="B33" s="53"/>
-      <c r="C33" s="145"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
+      <c r="C33" s="150"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="150"/>
+      <c r="G33" s="150"/>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
       <c r="J33" s="22"/>
@@ -27105,13 +27189,13 @@
       <c r="Y34" s="22"/>
     </row>
     <row r="35" spans="1:25" ht="12" customHeight="1">
-      <c r="A35" s="144" t="s">
+      <c r="A35" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -27292,11 +27376,11 @@
       <c r="Y40" s="22"/>
     </row>
     <row r="41" spans="1:25" ht="12">
-      <c r="A41" s="146" t="s">
+      <c r="A41" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -27321,14 +27405,14 @@
       <c r="Y41" s="22"/>
     </row>
     <row r="42" spans="1:25" ht="63.75" customHeight="1">
-      <c r="A42" s="147" t="s">
-        <v>317</v>
-      </c>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
+      <c r="A42" s="152" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" s="152"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
@@ -27621,21 +27705,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="date" prompt="Date in international format: YYYY-MM-DD" sqref="C12:D12" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -27961,13 +28045,30 @@
       <c r="B5" s="141">
         <v>0.05</v>
       </c>
-      <c r="C5" s="142"/>
+      <c r="C5" s="142">
+        <f>AVERAGE(A5:B5)</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="D5" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="62"/>
+        <v>299</v>
+      </c>
+      <c r="E5" s="62">
+        <v>0.9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.883</v>
+      </c>
+      <c r="G5" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="N5" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
@@ -27991,11 +28092,28 @@
       <c r="B6" s="142">
         <v>0.1</v>
       </c>
-      <c r="C6" s="142"/>
+      <c r="C6" s="142">
+        <f t="shared" ref="C6:C19" si="0">AVERAGE(A6:B6)</f>
+        <v>7.5000000000000011E-2</v>
+      </c>
       <c r="D6" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E6" s="62"/>
+        <v>300</v>
+      </c>
+      <c r="E6" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="G6" s="6">
+        <v>19.7</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -28018,11 +28136,28 @@
       <c r="B7" s="141">
         <v>0.15</v>
       </c>
-      <c r="C7" s="142"/>
+      <c r="C7" s="142">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
       <c r="D7" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E7" s="62"/>
+        <v>301</v>
+      </c>
+      <c r="E7" s="62">
+        <v>2.1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>3.91</v>
+      </c>
+      <c r="G7" s="6">
+        <v>19.3</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -28045,11 +28180,28 @@
       <c r="B8" s="142">
         <v>0.2</v>
       </c>
-      <c r="C8" s="142"/>
+      <c r="C8" s="142">
+        <f t="shared" si="0"/>
+        <v>0.17499999999999999</v>
+      </c>
       <c r="D8" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="62"/>
+        <v>302</v>
+      </c>
+      <c r="E8" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="6">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="G8" s="6">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>329</v>
+      </c>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -28072,11 +28224,28 @@
       <c r="B9" s="141">
         <v>0.25</v>
       </c>
-      <c r="C9" s="142"/>
+      <c r="C9" s="142">
+        <f t="shared" si="0"/>
+        <v>0.22500000000000001</v>
+      </c>
       <c r="D9" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E9" s="62"/>
+        <v>303</v>
+      </c>
+      <c r="E9" s="62">
+        <v>2.8</v>
+      </c>
+      <c r="F9" s="6">
+        <v>5.24</v>
+      </c>
+      <c r="G9" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>330</v>
+      </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
@@ -28099,11 +28268,28 @@
       <c r="B10" s="142">
         <v>0.3</v>
       </c>
-      <c r="C10" s="142"/>
+      <c r="C10" s="142">
+        <f t="shared" si="0"/>
+        <v>0.27500000000000002</v>
+      </c>
       <c r="D10" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E10" s="62"/>
+        <v>304</v>
+      </c>
+      <c r="E10" s="62">
+        <v>3.5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>6.44</v>
+      </c>
+      <c r="G10" s="6">
+        <v>19.7</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>331</v>
+      </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
@@ -28126,11 +28312,28 @@
       <c r="B11" s="141">
         <v>0.34</v>
       </c>
-      <c r="C11" s="142"/>
+      <c r="C11" s="142">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
       <c r="D11" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="62"/>
+        <v>305</v>
+      </c>
+      <c r="E11" s="62">
+        <v>3.8</v>
+      </c>
+      <c r="F11" s="6">
+        <v>6.89</v>
+      </c>
+      <c r="G11" s="6">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>332</v>
+      </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -28153,11 +28356,28 @@
       <c r="B12" s="142">
         <v>0.39</v>
       </c>
-      <c r="C12" s="142"/>
+      <c r="C12" s="142">
+        <f t="shared" si="0"/>
+        <v>0.36499999999999999</v>
+      </c>
       <c r="D12" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" s="62"/>
+        <v>306</v>
+      </c>
+      <c r="E12" s="62">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F12" s="6">
+        <v>7.47</v>
+      </c>
+      <c r="G12" s="6">
+        <v>19.7</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
@@ -28180,11 +28400,28 @@
       <c r="B13" s="142">
         <v>0.44</v>
       </c>
-      <c r="C13" s="142"/>
+      <c r="C13" s="142">
+        <f t="shared" si="0"/>
+        <v>0.41500000000000004</v>
+      </c>
       <c r="D13" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E13" s="62"/>
+        <v>307</v>
+      </c>
+      <c r="E13" s="62">
+        <v>4.2</v>
+      </c>
+      <c r="F13" s="6">
+        <v>7.58</v>
+      </c>
+      <c r="G13" s="6">
+        <v>19.3</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
@@ -28207,11 +28444,28 @@
       <c r="B14" s="142">
         <v>0.49</v>
       </c>
-      <c r="C14" s="142"/>
+      <c r="C14" s="142">
+        <f t="shared" si="0"/>
+        <v>0.46499999999999997</v>
+      </c>
       <c r="D14" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="62"/>
+        <v>308</v>
+      </c>
+      <c r="E14" s="62">
+        <v>3.9</v>
+      </c>
+      <c r="F14" s="6">
+        <v>7.18</v>
+      </c>
+      <c r="G14" s="6">
+        <v>19.3</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
@@ -28234,11 +28488,28 @@
       <c r="B15" s="142">
         <v>0.54</v>
       </c>
-      <c r="C15" s="142"/>
+      <c r="C15" s="142">
+        <f t="shared" si="0"/>
+        <v>0.51500000000000001</v>
+      </c>
       <c r="D15" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="E15" s="62"/>
+        <v>309</v>
+      </c>
+      <c r="E15" s="62">
+        <v>4.7</v>
+      </c>
+      <c r="F15" s="6">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="G15" s="6">
+        <v>20</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
@@ -28261,11 +28532,28 @@
       <c r="B16" s="142">
         <v>0.59</v>
       </c>
-      <c r="C16" s="142"/>
+      <c r="C16" s="142">
+        <f t="shared" si="0"/>
+        <v>0.56499999999999995</v>
+      </c>
       <c r="D16" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E16" s="62"/>
+        <v>310</v>
+      </c>
+      <c r="E16" s="62">
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="6">
+        <v>8.19</v>
+      </c>
+      <c r="G16" s="6">
+        <v>19.2</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>337</v>
+      </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
@@ -28288,11 +28576,28 @@
       <c r="B17" s="142">
         <v>0.64</v>
       </c>
-      <c r="C17" s="142"/>
+      <c r="C17" s="142">
+        <f t="shared" si="0"/>
+        <v>0.61499999999999999</v>
+      </c>
       <c r="D17" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="62"/>
+        <v>311</v>
+      </c>
+      <c r="E17" s="62">
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="6">
+        <v>8.06</v>
+      </c>
+      <c r="G17" s="6">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
@@ -28315,11 +28620,28 @@
       <c r="B18" s="142">
         <v>0.69</v>
       </c>
-      <c r="C18" s="142"/>
+      <c r="C18" s="142">
+        <f t="shared" si="0"/>
+        <v>0.66500000000000004</v>
+      </c>
       <c r="D18" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="E18" s="62"/>
+        <v>312</v>
+      </c>
+      <c r="E18" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F18" s="6">
+        <v>6.77</v>
+      </c>
+      <c r="G18" s="6">
+        <v>19.3</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
@@ -28342,11 +28664,28 @@
       <c r="B19" s="142">
         <v>0.74</v>
       </c>
-      <c r="C19" s="142"/>
+      <c r="C19" s="142">
+        <f t="shared" si="0"/>
+        <v>0.71499999999999997</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E19" s="62"/>
+        <v>313</v>
+      </c>
+      <c r="E19" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F19" s="6">
+        <v>6.71</v>
+      </c>
+      <c r="G19" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>340</v>
+      </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
@@ -28363,7 +28702,7 @@
       <c r="AB19" s="9"/>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="166"/>
+      <c r="A20" s="143"/>
       <c r="B20" s="142"/>
       <c r="C20" s="142"/>
       <c r="E20" s="62"/>
@@ -28383,7 +28722,7 @@
       <c r="AB20" s="9"/>
     </row>
     <row r="21" spans="1:28">
-      <c r="A21" s="166"/>
+      <c r="A21" s="143"/>
       <c r="B21" s="142"/>
       <c r="C21" s="142"/>
       <c r="E21" s="62"/>
@@ -28403,7 +28742,7 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="166"/>
+      <c r="A22" s="143"/>
       <c r="B22" s="142"/>
       <c r="C22" s="142"/>
       <c r="E22" s="62"/>
@@ -28423,7 +28762,7 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="166"/>
+      <c r="A23" s="143"/>
       <c r="B23" s="142"/>
       <c r="C23" s="142"/>
       <c r="E23" s="62"/>
@@ -28443,7 +28782,7 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28">
-      <c r="A24" s="166"/>
+      <c r="A24" s="143"/>
       <c r="B24" s="142"/>
       <c r="C24" s="142"/>
       <c r="E24" s="62"/>
@@ -28463,7 +28802,7 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28">
-      <c r="A25" s="166"/>
+      <c r="A25" s="143"/>
       <c r="B25" s="141"/>
       <c r="C25" s="142"/>
       <c r="E25" s="62"/>
@@ -28483,7 +28822,7 @@
       <c r="AB25" s="9"/>
     </row>
     <row r="26" spans="1:28">
-      <c r="A26" s="166"/>
+      <c r="A26" s="143"/>
       <c r="B26" s="142"/>
       <c r="C26" s="142"/>
       <c r="E26" s="62"/>
@@ -28849,8 +29188,8 @@
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="152"/>
-      <c r="F46" s="152"/>
+      <c r="E46" s="153"/>
+      <c r="F46" s="153"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -29046,9 +29385,9 @@
     <row r="4" spans="1:26" ht="15.6">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -29074,9 +29413,9 @@
     <row r="5" spans="1:26" ht="15.6">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -29102,9 +29441,9 @@
     <row r="6" spans="1:26" ht="15.6">
       <c r="A6" s="70"/>
       <c r="B6" s="70"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -29130,9 +29469,9 @@
     <row r="7" spans="1:26" ht="15.6">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -29158,9 +29497,9 @@
     <row r="8" spans="1:26" ht="15.6">
       <c r="A8" s="70"/>
       <c r="B8" s="70"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
@@ -29186,9 +29525,9 @@
     <row r="9" spans="1:26" ht="15.6">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
@@ -29214,9 +29553,9 @@
     <row r="10" spans="1:26" ht="15.6">
       <c r="A10" s="70"/>
       <c r="B10" s="70"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -29241,9 +29580,9 @@
     </row>
     <row r="11" spans="1:26" ht="15.6">
       <c r="A11" s="70"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -29269,9 +29608,9 @@
     <row r="12" spans="1:26" ht="15.6">
       <c r="A12" s="70"/>
       <c r="B12" s="70"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
@@ -29297,9 +29636,9 @@
     <row r="13" spans="1:26" ht="15.6">
       <c r="A13" s="70"/>
       <c r="B13" s="70"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
@@ -29325,9 +29664,9 @@
     <row r="14" spans="1:26" ht="15.6">
       <c r="A14" s="70"/>
       <c r="B14" s="70"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="153"/>
-      <c r="E14" s="153"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
@@ -29351,9 +29690,9 @@
       <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -29379,9 +29718,9 @@
     <row r="16" spans="1:26" ht="15.6">
       <c r="A16" s="70"/>
       <c r="B16" s="70"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -29407,9 +29746,9 @@
     <row r="17" spans="1:26" ht="15.6">
       <c r="A17" s="70"/>
       <c r="B17" s="70"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -29435,9 +29774,9 @@
     <row r="18" spans="1:26" ht="15.6">
       <c r="A18" s="70"/>
       <c r="B18" s="70"/>
-      <c r="C18" s="153"/>
-      <c r="D18" s="153"/>
-      <c r="E18" s="153"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
@@ -29463,9 +29802,9 @@
     <row r="19" spans="1:26" ht="15.6">
       <c r="A19" s="70"/>
       <c r="B19" s="70"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="153"/>
-      <c r="E19" s="153"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="156"/>
+      <c r="E19" s="156"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
@@ -29491,9 +29830,9 @@
     <row r="20" spans="1:26" ht="15.6">
       <c r="A20" s="70"/>
       <c r="B20" s="70"/>
-      <c r="C20" s="153"/>
-      <c r="D20" s="153"/>
-      <c r="E20" s="153"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="156"/>
+      <c r="E20" s="156"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -29519,9 +29858,9 @@
     <row r="21" spans="1:26" ht="15.6">
       <c r="A21" s="70"/>
       <c r="B21" s="70"/>
-      <c r="C21" s="153"/>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="156"/>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -29547,9 +29886,9 @@
     <row r="22" spans="1:26" ht="15.6">
       <c r="A22" s="70"/>
       <c r="B22" s="70"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -29575,9 +29914,9 @@
     <row r="23" spans="1:26" ht="15.6">
       <c r="A23" s="70"/>
       <c r="B23" s="70"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -29603,9 +29942,9 @@
     <row r="24" spans="1:26" ht="15.6">
       <c r="A24" s="70"/>
       <c r="B24" s="70"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="156"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -29631,9 +29970,9 @@
     <row r="25" spans="1:26" ht="15.6">
       <c r="A25" s="70"/>
       <c r="B25" s="70"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
@@ -29659,9 +29998,9 @@
     <row r="26" spans="1:26" ht="15.6">
       <c r="A26" s="70"/>
       <c r="B26" s="70"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
+      <c r="C26" s="156"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
@@ -29687,9 +30026,9 @@
     <row r="27" spans="1:26" ht="15.6">
       <c r="A27" s="70"/>
       <c r="B27" s="70"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
@@ -29715,9 +30054,9 @@
     <row r="28" spans="1:26" ht="15.6">
       <c r="A28" s="70"/>
       <c r="B28" s="70"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
+      <c r="C28" s="156"/>
+      <c r="D28" s="156"/>
+      <c r="E28" s="156"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -29743,9 +30082,9 @@
     <row r="29" spans="1:26" ht="15.6">
       <c r="A29" s="70"/>
       <c r="B29" s="70"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
@@ -29771,9 +30110,9 @@
     <row r="30" spans="1:26" ht="15.6">
       <c r="A30" s="70"/>
       <c r="B30" s="70"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
@@ -29799,9 +30138,9 @@
     <row r="31" spans="1:26" ht="15.6">
       <c r="A31" s="70"/>
       <c r="B31" s="70"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
@@ -29827,9 +30166,9 @@
     <row r="32" spans="1:26" ht="15.6">
       <c r="A32" s="70"/>
       <c r="B32" s="70"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
@@ -29855,9 +30194,9 @@
     <row r="33" spans="1:26" ht="15.6">
       <c r="A33" s="70"/>
       <c r="B33" s="70"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
+      <c r="C33" s="156"/>
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -29883,9 +30222,9 @@
     <row r="34" spans="1:26" ht="15.6">
       <c r="A34" s="70"/>
       <c r="B34" s="70"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="153"/>
+      <c r="C34" s="156"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="156"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -29911,9 +30250,9 @@
     <row r="35" spans="1:26" ht="15.6">
       <c r="A35" s="70"/>
       <c r="B35" s="70"/>
-      <c r="C35" s="153"/>
-      <c r="D35" s="153"/>
-      <c r="E35" s="153"/>
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -29939,9 +30278,9 @@
     <row r="36" spans="1:26" ht="15.6">
       <c r="A36" s="70"/>
       <c r="B36" s="70"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
       <c r="F36" s="22"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -29967,9 +30306,9 @@
     <row r="37" spans="1:26" ht="15.6">
       <c r="A37" s="70"/>
       <c r="B37" s="70"/>
-      <c r="C37" s="153"/>
-      <c r="D37" s="153"/>
-      <c r="E37" s="153"/>
+      <c r="C37" s="156"/>
+      <c r="D37" s="156"/>
+      <c r="E37" s="156"/>
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -29995,9 +30334,9 @@
     <row r="38" spans="1:26" ht="15.6">
       <c r="A38" s="70"/>
       <c r="B38" s="70"/>
-      <c r="C38" s="153"/>
-      <c r="D38" s="153"/>
-      <c r="E38" s="153"/>
+      <c r="C38" s="156"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
       <c r="F38" s="22"/>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -30023,9 +30362,9 @@
     <row r="39" spans="1:26" ht="15.6">
       <c r="A39" s="70"/>
       <c r="B39" s="70"/>
-      <c r="C39" s="153"/>
-      <c r="D39" s="153"/>
-      <c r="E39" s="153"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
       <c r="F39" s="22"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -30078,36 +30417,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C39:E39"/>
@@ -30116,6 +30425,36 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -30269,10 +30608,10 @@
       <c r="C4" s="6">
         <v>0.1</v>
       </c>
-      <c r="D4" s="156" t="s">
+      <c r="D4" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="156"/>
+      <c r="E4" s="159"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -30301,10 +30640,10 @@
       <c r="B5" s="6">
         <v>0.1</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
       <c r="F5" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -30334,10 +30673,10 @@
       <c r="B6" s="6">
         <v>0.3</v>
       </c>
-      <c r="D6" s="156" t="s">
+      <c r="D6" s="159" t="s">
         <v>281</v>
       </c>
-      <c r="E6" s="156"/>
+      <c r="E6" s="159"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -30367,10 +30706,10 @@
         <v>0.3</v>
       </c>
       <c r="C7"/>
-      <c r="D7" s="156" t="s">
+      <c r="D7" s="159" t="s">
         <v>259</v>
       </c>
-      <c r="E7" s="156"/>
+      <c r="E7" s="159"/>
       <c r="F7"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -30395,8 +30734,8 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="62"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -30420,8 +30759,8 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="62"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -30445,8 +30784,8 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="62"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -30470,8 +30809,8 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="62"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -30495,8 +30834,8 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="62"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -30520,8 +30859,8 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="62"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -30545,8 +30884,8 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="62"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -30570,8 +30909,8 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="62"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="159"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -30595,8 +30934,8 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="62"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
+      <c r="D16" s="159"/>
+      <c r="E16" s="159"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -30620,8 +30959,8 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="62"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
+      <c r="D17" s="159"/>
+      <c r="E17" s="159"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -30645,8 +30984,8 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="62"/>
-      <c r="D18" s="156"/>
-      <c r="E18" s="156"/>
+      <c r="D18" s="159"/>
+      <c r="E18" s="159"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -30670,8 +31009,8 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="62"/>
-      <c r="D19" s="156"/>
-      <c r="E19" s="156"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -30695,8 +31034,8 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="62"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156"/>
+      <c r="D20" s="159"/>
+      <c r="E20" s="159"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -30720,8 +31059,8 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="62"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
+      <c r="D21" s="159"/>
+      <c r="E21" s="159"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -30745,8 +31084,8 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="62"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -30770,8 +31109,8 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="62"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="159"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -30796,8 +31135,8 @@
     <row r="24" spans="1:26">
       <c r="A24" s="62"/>
       <c r="B24" s="62"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -30821,8 +31160,8 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="62"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -30848,8 +31187,8 @@
       <c r="A26" s="62"/>
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
       <c r="F26" s="59"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -30876,8 +31215,8 @@
       <c r="A27" s="62"/>
       <c r="B27" s="59"/>
       <c r="C27" s="59"/>
-      <c r="D27" s="156"/>
-      <c r="E27" s="156"/>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
       <c r="F27" s="59"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -30902,8 +31241,8 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="62"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
+      <c r="D28" s="159"/>
+      <c r="E28" s="159"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -30927,8 +31266,8 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="62"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="159"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -30952,8 +31291,8 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="62"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
+      <c r="D30" s="159"/>
+      <c r="E30" s="159"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -30977,8 +31316,8 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="62"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="159"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -31002,8 +31341,8 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="62"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
+      <c r="D32" s="159"/>
+      <c r="E32" s="159"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -31027,8 +31366,8 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="62"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -31052,8 +31391,8 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="62"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
+      <c r="D34" s="159"/>
+      <c r="E34" s="159"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -31077,8 +31416,8 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="62"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="159"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -31102,8 +31441,8 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="62"/>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156"/>
+      <c r="D36" s="159"/>
+      <c r="E36" s="159"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -31127,8 +31466,8 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="62"/>
-      <c r="D37" s="156"/>
-      <c r="E37" s="156"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="159"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -31152,8 +31491,8 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="62"/>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
+      <c r="D38" s="159"/>
+      <c r="E38" s="159"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -31177,8 +31516,8 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="62"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="156"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -31202,8 +31541,8 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="62"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
+      <c r="D40" s="159"/>
+      <c r="E40" s="159"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -31227,8 +31566,8 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="62"/>
-      <c r="D41" s="156"/>
-      <c r="E41" s="156"/>
+      <c r="D41" s="159"/>
+      <c r="E41" s="159"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -31252,8 +31591,8 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="62"/>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
+      <c r="D42" s="159"/>
+      <c r="E42" s="159"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -31277,8 +31616,8 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43" s="62"/>
-      <c r="D43" s="156"/>
-      <c r="E43" s="156"/>
+      <c r="D43" s="159"/>
+      <c r="E43" s="159"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -31302,8 +31641,8 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44" s="62"/>
-      <c r="D44" s="156"/>
-      <c r="E44" s="156"/>
+      <c r="D44" s="159"/>
+      <c r="E44" s="159"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -31327,8 +31666,8 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45" s="62"/>
-      <c r="D45" s="156"/>
-      <c r="E45" s="156"/>
+      <c r="D45" s="159"/>
+      <c r="E45" s="159"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -31352,8 +31691,8 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="62"/>
-      <c r="D46" s="156"/>
-      <c r="E46" s="156"/>
+      <c r="D46" s="159"/>
+      <c r="E46" s="159"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -31379,8 +31718,8 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
@@ -31405,52 +31744,52 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -32565,7 +32904,7 @@
         <v>151</v>
       </c>
       <c r="G3" s="60" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H3" s="61" t="s">
         <v>1</v>
@@ -33487,58 +33826,58 @@
       <c r="E2" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="161" t="s">
+      <c r="F2" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161" t="s">
+      <c r="G2" s="160"/>
+      <c r="H2" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="161"/>
-      <c r="J2" s="162" t="s">
+      <c r="I2" s="160"/>
+      <c r="J2" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="162"/>
-      <c r="L2" s="161" t="s">
+      <c r="K2" s="161"/>
+      <c r="L2" s="160" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162" t="s">
+      <c r="M2" s="160"/>
+      <c r="N2" s="161" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="162"/>
-      <c r="P2" s="160" t="s">
+      <c r="O2" s="161"/>
+      <c r="P2" s="163" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="160"/>
+      <c r="Q2" s="163"/>
       <c r="R2" s="157" t="s">
         <v>128</v>
       </c>
       <c r="S2" s="157"/>
-      <c r="T2" s="160" t="s">
+      <c r="T2" s="163" t="s">
         <v>129</v>
       </c>
-      <c r="U2" s="160"/>
+      <c r="U2" s="163"/>
       <c r="V2" s="157" t="s">
         <v>130</v>
       </c>
       <c r="W2" s="157"/>
-      <c r="X2" s="160" t="s">
+      <c r="X2" s="163" t="s">
         <v>131</v>
       </c>
-      <c r="Y2" s="160"/>
-      <c r="Z2" s="159" t="s">
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="162" t="s">
         <v>132</v>
       </c>
-      <c r="AA2" s="159"/>
-      <c r="AB2" s="159" t="s">
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="162" t="s">
         <v>133</v>
       </c>
-      <c r="AC2" s="159"/>
-      <c r="AD2" s="160" t="s">
+      <c r="AC2" s="162"/>
+      <c r="AD2" s="163" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="160"/>
+      <c r="AE2" s="163"/>
       <c r="AF2" s="58" t="s">
         <v>95</v>
       </c>
@@ -34909,11 +35248,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
@@ -34922,6 +35256,11 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0700-000000000000}">
